--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/151.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/151.xlsx
@@ -426,13 +426,13 @@
         <v>-2.125089097407627</v>
       </c>
       <c r="E2">
-        <v>-15.30164782151562</v>
+        <v>-15.07241193877334</v>
       </c>
       <c r="F2">
-        <v>-0.7776722933630864</v>
+        <v>-0.8867343172482666</v>
       </c>
       <c r="G2">
-        <v>-7.378631122779977</v>
+        <v>-6.829391754541651</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.085227386722901</v>
       </c>
       <c r="E3">
-        <v>-15.39041044053997</v>
+        <v>-15.38380339696278</v>
       </c>
       <c r="F3">
-        <v>-0.9409426800874662</v>
+        <v>-0.9749794683010951</v>
       </c>
       <c r="G3">
-        <v>-7.459176695750445</v>
+        <v>-7.005426703046857</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.206775828582238</v>
       </c>
       <c r="E4">
-        <v>-15.18099116005525</v>
+        <v>-16.06210540467569</v>
       </c>
       <c r="F4">
-        <v>-1.096800835291596</v>
+        <v>-0.7920179600447682</v>
       </c>
       <c r="G4">
-        <v>-7.801546694330792</v>
+        <v>-7.069982341062645</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.350736661187109</v>
       </c>
       <c r="E5">
-        <v>-17.25970111227019</v>
+        <v>-16.85142748116065</v>
       </c>
       <c r="F5">
-        <v>-1.28366726748472</v>
+        <v>-0.6590765890390868</v>
       </c>
       <c r="G5">
-        <v>-7.764008418460996</v>
+        <v>-7.230987412819561</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.489467704840123</v>
       </c>
       <c r="E6">
-        <v>-16.35167414662217</v>
+        <v>-17.86182513022607</v>
       </c>
       <c r="F6">
-        <v>-1.41482102163516</v>
+        <v>-0.5502812994576082</v>
       </c>
       <c r="G6">
-        <v>-7.175625159766328</v>
+        <v>-6.967706347172402</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.542256424242742</v>
       </c>
       <c r="E7">
-        <v>-16.9954510685006</v>
+        <v>-17.17513638865095</v>
       </c>
       <c r="F7">
-        <v>-1.13067360675947</v>
+        <v>-0.4324319541635309</v>
       </c>
       <c r="G7">
-        <v>-7.005526019413035</v>
+        <v>-7.301862882269817</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.460479708266684</v>
       </c>
       <c r="E8">
-        <v>-18.7168417791403</v>
+        <v>-18.91197372413082</v>
       </c>
       <c r="F8">
-        <v>-0.9647317351610624</v>
+        <v>-0.3773562906536002</v>
       </c>
       <c r="G8">
-        <v>-6.854906129012814</v>
+        <v>-6.653571991496498</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.177992954268699</v>
       </c>
       <c r="E9">
-        <v>-19.09525918111727</v>
+        <v>-20.04139325553983</v>
       </c>
       <c r="F9">
-        <v>-1.044970715265834</v>
+        <v>-0.2822033838288265</v>
       </c>
       <c r="G9">
-        <v>-5.64120054449629</v>
+        <v>-6.853780543529462</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.645798291749692</v>
       </c>
       <c r="E10">
-        <v>-18.64346238632001</v>
+        <v>-19.93073999316241</v>
       </c>
       <c r="F10">
-        <v>-1.146208809031573</v>
+        <v>-0.4494300532689767</v>
       </c>
       <c r="G10">
-        <v>-5.720286166883939</v>
+        <v>-5.954642996154486</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.821086755777893</v>
       </c>
       <c r="E11">
-        <v>-19.07222736231425</v>
+        <v>-21.20369403671855</v>
       </c>
       <c r="F11">
-        <v>-0.9220931798367634</v>
+        <v>-0.03690805687923972</v>
       </c>
       <c r="G11">
-        <v>-6.751696561280496</v>
+        <v>-6.101459069730085</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.679805463512968</v>
       </c>
       <c r="E12">
-        <v>-20.17698029580349</v>
+        <v>-22.02909446562262</v>
       </c>
       <c r="F12">
-        <v>-0.7028541495422351</v>
+        <v>-0.148365719293316</v>
       </c>
       <c r="G12">
-        <v>-5.880486776074812</v>
+        <v>-5.918567981413048</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.208436042366603</v>
       </c>
       <c r="E13">
-        <v>-21.17159168447817</v>
+        <v>-22.07096926477154</v>
       </c>
       <c r="F13">
-        <v>-0.4238906578732652</v>
+        <v>0.09816636018865046</v>
       </c>
       <c r="G13">
-        <v>-4.903981779447068</v>
+        <v>-5.296314531306097</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.417523163492815</v>
       </c>
       <c r="E14">
-        <v>-22.89675914244027</v>
+        <v>-22.85443602436458</v>
       </c>
       <c r="F14">
-        <v>-0.4455980256636262</v>
+        <v>0.3064444330093358</v>
       </c>
       <c r="G14">
-        <v>-5.192833498839557</v>
+        <v>-4.89389123664337</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.337947703625207</v>
       </c>
       <c r="E15">
-        <v>-23.06910380622419</v>
+        <v>-22.7871429006106</v>
       </c>
       <c r="F15">
-        <v>-0.5188952869329376</v>
+        <v>0.1603949762217549</v>
       </c>
       <c r="G15">
-        <v>-3.489028131598249</v>
+        <v>-3.067605616085644</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.00987297913076</v>
       </c>
       <c r="E16">
-        <v>-23.93912781799984</v>
+        <v>-24.58486104064959</v>
       </c>
       <c r="F16">
-        <v>0.4463739114250339</v>
+        <v>0.9671759528717082</v>
       </c>
       <c r="G16">
-        <v>-5.126427265867317</v>
+        <v>-3.33339938579711</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.494948134489984</v>
       </c>
       <c r="E17">
-        <v>-24.87329313562014</v>
+        <v>-25.04308374006373</v>
       </c>
       <c r="F17">
-        <v>-0.2771975596137091</v>
+        <v>0.3946962110013867</v>
       </c>
       <c r="G17">
-        <v>-2.565127703589524</v>
+        <v>-3.197706745233463</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.857702901684514</v>
       </c>
       <c r="E18">
-        <v>-26.1045218196696</v>
+        <v>-27.56067075073203</v>
       </c>
       <c r="F18">
-        <v>0.1454619970514882</v>
+        <v>0.735413664181657</v>
       </c>
       <c r="G18">
-        <v>-3.195015271710035</v>
+        <v>-3.329343967511503</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.16638817112063</v>
       </c>
       <c r="E19">
-        <v>-25.91824304136408</v>
+        <v>-26.66894629151163</v>
       </c>
       <c r="F19">
-        <v>0.236383603182762</v>
+        <v>0.9163854339364593</v>
       </c>
       <c r="G19">
-        <v>-2.784759226301392</v>
+        <v>-1.841025319966894</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.5028675820220079</v>
       </c>
       <c r="E20">
-        <v>-26.31277728233434</v>
+        <v>-27.77623969891917</v>
       </c>
       <c r="F20">
-        <v>0.5566494935553152</v>
+        <v>1.423425807720426</v>
       </c>
       <c r="G20">
-        <v>-1.834894189628164</v>
+        <v>-1.616861660411764</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.089666570494404</v>
       </c>
       <c r="E21">
-        <v>-27.17174276058326</v>
+        <v>-28.54648784288382</v>
       </c>
       <c r="F21">
-        <v>0.9299077034197585</v>
+        <v>1.354919823508906</v>
       </c>
       <c r="G21">
-        <v>-2.455234144413417</v>
+        <v>-2.327453707688628</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.530408316695077</v>
       </c>
       <c r="E22">
-        <v>-27.73430150113413</v>
+        <v>-28.85857668607044</v>
       </c>
       <c r="F22">
-        <v>0.7444014505020315</v>
+        <v>1.20159564418994</v>
       </c>
       <c r="G22">
-        <v>-1.002616419964309</v>
+        <v>-1.440220882072871</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.773243997381096</v>
       </c>
       <c r="E23">
-        <v>-28.37501264610937</v>
+        <v>-29.93248618309343</v>
       </c>
       <c r="F23">
-        <v>0.8505898678669002</v>
+        <v>1.543580499496494</v>
       </c>
       <c r="G23">
-        <v>-1.435202095035336</v>
+        <v>-1.035466963350497</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.790464557354039</v>
       </c>
       <c r="E24">
-        <v>-29.77923582996285</v>
+        <v>-29.40958328942773</v>
       </c>
       <c r="F24">
-        <v>1.520245389759632</v>
+        <v>1.919886273035836</v>
       </c>
       <c r="G24">
-        <v>-1.221314368834103</v>
+        <v>-1.5304829062011</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.552569325056237</v>
       </c>
       <c r="E25">
-        <v>-30.05794076276493</v>
+        <v>-30.3815749504341</v>
       </c>
       <c r="F25">
-        <v>0.9434382565770856</v>
+        <v>2.043624482196416</v>
       </c>
       <c r="G25">
-        <v>-0.8458488464976615</v>
+        <v>-0.6022688373547054</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.05218163683186</v>
       </c>
       <c r="E26">
-        <v>-30.20548976711984</v>
+        <v>-30.8973341763527</v>
       </c>
       <c r="F26">
-        <v>0.7814211897331415</v>
+        <v>2.118416118260377</v>
       </c>
       <c r="G26">
-        <v>-0.1219649588806237</v>
+        <v>-0.3861200085501503</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.294242712481512</v>
       </c>
       <c r="E27">
-        <v>-29.52164037874754</v>
+        <v>-32.10392796180043</v>
       </c>
       <c r="F27">
-        <v>1.269187110788769</v>
+        <v>2.312182850918821</v>
       </c>
       <c r="G27">
-        <v>-1.088816404715852</v>
+        <v>-0.5888809911938927</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.29319616702776</v>
       </c>
       <c r="E28">
-        <v>-30.79580805333773</v>
+        <v>-31.28317374722823</v>
       </c>
       <c r="F28">
-        <v>1.331163903131422</v>
+        <v>1.511176423433783</v>
       </c>
       <c r="G28">
-        <v>-1.868185035571075</v>
+        <v>-0.792972813144422</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.078013945984423</v>
       </c>
       <c r="E29">
-        <v>-27.44277192994234</v>
+        <v>-31.32472928895962</v>
       </c>
       <c r="F29">
-        <v>1.070642354950978</v>
+        <v>2.128712725077175</v>
       </c>
       <c r="G29">
-        <v>-0.6587235704358969</v>
+        <v>-1.043442067554601</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.677120613709215</v>
       </c>
       <c r="E30">
-        <v>-30.21179566717553</v>
+        <v>-30.67766695918862</v>
       </c>
       <c r="F30">
-        <v>0.885155982850918</v>
+        <v>1.573885492560511</v>
       </c>
       <c r="G30">
-        <v>-1.729453314202377</v>
+        <v>-1.049910873538337</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.12168411897383</v>
       </c>
       <c r="E31">
-        <v>-29.03676308132425</v>
+        <v>-30.1791883900833</v>
       </c>
       <c r="F31">
-        <v>1.256365640128238</v>
+        <v>1.655665236034489</v>
       </c>
       <c r="G31">
-        <v>-1.549644343782402</v>
+        <v>-1.468499562069326</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.437914648970274</v>
       </c>
       <c r="E32">
-        <v>-30.58707483666518</v>
+        <v>-29.84745955512541</v>
       </c>
       <c r="F32">
-        <v>1.150866424442499</v>
+        <v>1.623877465319461</v>
       </c>
       <c r="G32">
-        <v>-0.7901654705271202</v>
+        <v>-1.544764599657516</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.651045841925439</v>
       </c>
       <c r="E33">
-        <v>-28.90083640551002</v>
+        <v>-30.70283848196026</v>
       </c>
       <c r="F33">
-        <v>1.41726938118282</v>
+        <v>1.552853244203432</v>
       </c>
       <c r="G33">
-        <v>-0.5096894313489866</v>
+        <v>-1.458097827984935</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.785446691338938</v>
       </c>
       <c r="E34">
-        <v>-29.17989003081068</v>
+        <v>-30.58494871811858</v>
       </c>
       <c r="F34">
-        <v>1.027772685121298</v>
+        <v>1.356215390126885</v>
       </c>
       <c r="G34">
-        <v>-2.480516780696831</v>
+        <v>-1.925066829026833</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.855784857250331</v>
       </c>
       <c r="E35">
-        <v>-28.37204649563435</v>
+        <v>-28.35220272253273</v>
       </c>
       <c r="F35">
-        <v>1.703467005380437</v>
+        <v>2.084120051049672</v>
       </c>
       <c r="G35">
-        <v>-3.171596472565231</v>
+        <v>-1.844560982602836</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.885632793536342</v>
       </c>
       <c r="E36">
-        <v>-27.65331880045496</v>
+        <v>-29.34824058051983</v>
       </c>
       <c r="F36">
-        <v>1.24995407643057</v>
+        <v>1.770037923339017</v>
       </c>
       <c r="G36">
-        <v>-2.355599965863512</v>
+        <v>-2.783802478640543</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.8946276386111733</v>
       </c>
       <c r="E37">
-        <v>-28.56394511018339</v>
+        <v>-28.82186887576426</v>
       </c>
       <c r="F37">
-        <v>1.821467941909227</v>
+        <v>2.136563991320909</v>
       </c>
       <c r="G37">
-        <v>-2.374287995432697</v>
+        <v>-2.00556936490529</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.09998821348483815</v>
       </c>
       <c r="E38">
-        <v>-27.55831594424805</v>
+        <v>-28.49460511617794</v>
       </c>
       <c r="F38">
-        <v>1.107009340668682</v>
+        <v>2.337582252223459</v>
       </c>
       <c r="G38">
-        <v>-1.370467687560427</v>
+        <v>-2.567210036733726</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.07302941026827</v>
       </c>
       <c r="E39">
-        <v>-26.05012578988946</v>
+        <v>-28.31682175511081</v>
       </c>
       <c r="F39">
-        <v>1.555979502781597</v>
+        <v>2.185182530926017</v>
       </c>
       <c r="G39">
-        <v>-2.257187378617597</v>
+        <v>-2.592499294108218</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.008331872107315</v>
       </c>
       <c r="E40">
-        <v>-26.35816164883922</v>
+        <v>-28.04174412998888</v>
       </c>
       <c r="F40">
-        <v>1.776817282163528</v>
+        <v>2.152947441813478</v>
       </c>
       <c r="G40">
-        <v>-2.595617828006212</v>
+        <v>-2.943883908192001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.888734955979583</v>
       </c>
       <c r="E41">
-        <v>-23.1062463500351</v>
+        <v>-26.12429313718709</v>
       </c>
       <c r="F41">
-        <v>1.300335381868836</v>
+        <v>2.015181659053892</v>
       </c>
       <c r="G41">
-        <v>-3.583759392204493</v>
+        <v>-3.389261531226772</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.696439950278651</v>
       </c>
       <c r="E42">
-        <v>-24.92869901510398</v>
+        <v>-25.72109139696614</v>
       </c>
       <c r="F42">
-        <v>1.657626810044319</v>
+        <v>2.259747194321612</v>
       </c>
       <c r="G42">
-        <v>-3.627316239864685</v>
+        <v>-2.948790136681201</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.430097988609844</v>
       </c>
       <c r="E43">
-        <v>-22.8925838894052</v>
+        <v>-26.20638531399814</v>
       </c>
       <c r="F43">
-        <v>1.151827330629746</v>
+        <v>2.420042913702539</v>
       </c>
       <c r="G43">
-        <v>-2.777671348301813</v>
+        <v>-3.397729906716228</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.082997824808601</v>
       </c>
       <c r="E44">
-        <v>-24.55017292975083</v>
+        <v>-24.6061222261156</v>
       </c>
       <c r="F44">
-        <v>1.998591116710623</v>
+        <v>2.292678112052504</v>
       </c>
       <c r="G44">
-        <v>-2.819407395915405</v>
+        <v>-3.680324695039495</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.650057953438626</v>
       </c>
       <c r="E45">
-        <v>-23.15538934996634</v>
+        <v>-24.54669053323894</v>
       </c>
       <c r="F45">
-        <v>1.752532863383058</v>
+        <v>2.485251995650916</v>
       </c>
       <c r="G45">
-        <v>-2.333869544943735</v>
+        <v>-2.927738377596976</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.138982138402121</v>
       </c>
       <c r="E46">
-        <v>-22.68355858615915</v>
+        <v>-23.27732756957088</v>
       </c>
       <c r="F46">
-        <v>2.366977697879202</v>
+        <v>2.539821526677736</v>
       </c>
       <c r="G46">
-        <v>-2.94243719979134</v>
+        <v>-2.46748316290872</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.552214524157398</v>
       </c>
       <c r="E47">
-        <v>-21.27125434043898</v>
+        <v>-23.69329960649346</v>
       </c>
       <c r="F47">
-        <v>1.701881510171479</v>
+        <v>2.528315503452851</v>
       </c>
       <c r="G47">
-        <v>-2.952951492424065</v>
+        <v>-3.536137194622078</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.894410482248247</v>
       </c>
       <c r="E48">
-        <v>-20.42954687663329</v>
+        <v>-23.55143610125517</v>
       </c>
       <c r="F48">
-        <v>2.272043480048768</v>
+        <v>2.348417297852077</v>
       </c>
       <c r="G48">
-        <v>-3.323398227722972</v>
+        <v>-3.178303637827794</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.179013018481992</v>
       </c>
       <c r="E49">
-        <v>-21.20027503884276</v>
+        <v>-22.11701026000753</v>
       </c>
       <c r="F49">
-        <v>1.515990894778853</v>
+        <v>2.40257927211672</v>
       </c>
       <c r="G49">
-        <v>-3.649308193882063</v>
+        <v>-2.963095003956392</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.411930898002145</v>
       </c>
       <c r="E50">
-        <v>-18.5263832193257</v>
+        <v>-21.33427258472972</v>
       </c>
       <c r="F50">
-        <v>2.415568072992616</v>
+        <v>2.479327511986094</v>
       </c>
       <c r="G50">
-        <v>-2.26939336002089</v>
+        <v>-3.900568668676128</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.601718680558378</v>
       </c>
       <c r="E51">
-        <v>-21.0147434587485</v>
+        <v>-21.59200162592827</v>
       </c>
       <c r="F51">
-        <v>2.025108814009041</v>
+        <v>2.731194277542089</v>
       </c>
       <c r="G51">
-        <v>-3.776449695317773</v>
+        <v>-3.915535645059173</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.762535390447077</v>
       </c>
       <c r="E52">
-        <v>-18.84496589423932</v>
+        <v>-21.06966026303952</v>
       </c>
       <c r="F52">
-        <v>2.217353007381139</v>
+        <v>2.443117916074922</v>
       </c>
       <c r="G52">
-        <v>-2.911278345175719</v>
+        <v>-3.555791903488731</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.895381135503549</v>
       </c>
       <c r="E53">
-        <v>-17.51656068645926</v>
+        <v>-19.60675032028363</v>
       </c>
       <c r="F53">
-        <v>2.170800416078612</v>
+        <v>2.429749722928543</v>
       </c>
       <c r="G53">
-        <v>-4.40276518480141</v>
+        <v>-3.401493996994379</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.008954594154313</v>
       </c>
       <c r="E54">
-        <v>-17.79657434824955</v>
+        <v>-19.84042863602744</v>
       </c>
       <c r="F54">
-        <v>1.797102343123282</v>
+        <v>2.51091647452445</v>
       </c>
       <c r="G54">
-        <v>-4.163803386685737</v>
+        <v>-3.774407088720042</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.112701734992553</v>
       </c>
       <c r="E55">
-        <v>-15.91848485152243</v>
+        <v>-19.33828879568691</v>
       </c>
       <c r="F55">
-        <v>2.01494143250708</v>
+        <v>2.712877417531387</v>
       </c>
       <c r="G55">
-        <v>-3.598825684953717</v>
+        <v>-4.83956187379839</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.201917621355998</v>
       </c>
       <c r="E56">
-        <v>-17.09108338259458</v>
+        <v>-18.58458316727228</v>
       </c>
       <c r="F56">
-        <v>2.365079079791986</v>
+        <v>2.315897250352974</v>
       </c>
       <c r="G56">
-        <v>-4.766984783940948</v>
+        <v>-4.88634981390491</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.281967948334072</v>
       </c>
       <c r="E57">
-        <v>-17.4987547266611</v>
+        <v>-17.21892673230512</v>
       </c>
       <c r="F57">
-        <v>2.087725105986655</v>
+        <v>2.577942994554569</v>
       </c>
       <c r="G57">
-        <v>-4.023005884900534</v>
+        <v>-5.118673968214344</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.352171439127936</v>
       </c>
       <c r="E58">
-        <v>-15.778903697184</v>
+        <v>-18.57463863835144</v>
       </c>
       <c r="F58">
-        <v>1.871032477088333</v>
+        <v>2.428879937155604</v>
       </c>
       <c r="G58">
-        <v>-4.261845192831253</v>
+        <v>-5.114174936826474</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.402659362690187</v>
       </c>
       <c r="E59">
-        <v>-16.75239881156092</v>
+        <v>-16.12333943020741</v>
       </c>
       <c r="F59">
-        <v>2.187919456824867</v>
+        <v>2.549619456318049</v>
       </c>
       <c r="G59">
-        <v>-5.877477490179614</v>
+        <v>-5.713343952888088</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.434559302563253</v>
       </c>
       <c r="E60">
-        <v>-15.09665738861041</v>
+        <v>-16.33529465613642</v>
       </c>
       <c r="F60">
-        <v>2.17383555424247</v>
+        <v>2.466043812314801</v>
       </c>
       <c r="G60">
-        <v>-5.567401863334857</v>
+        <v>-4.936074207904763</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.43841346366181</v>
       </c>
       <c r="E61">
-        <v>-16.1990826864597</v>
+        <v>-16.62565135256023</v>
       </c>
       <c r="F61">
-        <v>1.476040391676639</v>
+        <v>2.736022002765604</v>
       </c>
       <c r="G61">
-        <v>-4.862106688920827</v>
+        <v>-5.606108761780016</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.402475275342907</v>
       </c>
       <c r="E62">
-        <v>-14.22592693488956</v>
+        <v>-15.60789946170636</v>
       </c>
       <c r="F62">
-        <v>1.649560168275857</v>
+        <v>2.338819833123241</v>
       </c>
       <c r="G62">
-        <v>-5.097039553115207</v>
+        <v>-5.417811552597349</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.326327965964543</v>
       </c>
       <c r="E63">
-        <v>-15.33046250162643</v>
+        <v>-15.05540751887454</v>
       </c>
       <c r="F63">
-        <v>1.574158853803435</v>
+        <v>2.245548977037628</v>
       </c>
       <c r="G63">
-        <v>-4.244617113844886</v>
+        <v>-6.139619728161263</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.197383829253649</v>
       </c>
       <c r="E64">
-        <v>-14.50297897467883</v>
+        <v>-14.17392193938548</v>
       </c>
       <c r="F64">
-        <v>2.3910334872565</v>
+        <v>1.918711648058667</v>
       </c>
       <c r="G64">
-        <v>-5.596581011717993</v>
+        <v>-5.941933811829224</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.009420923855004</v>
       </c>
       <c r="E65">
-        <v>-13.54415611608677</v>
+        <v>-15.6212086468149</v>
       </c>
       <c r="F65">
-        <v>2.269414241912282</v>
+        <v>2.48872119833384</v>
       </c>
       <c r="G65">
-        <v>-5.186447456494303</v>
+        <v>-6.241902343142586</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.762939688845429</v>
       </c>
       <c r="E66">
-        <v>-14.07852057746588</v>
+        <v>-15.59031086866056</v>
       </c>
       <c r="F66">
-        <v>1.706306648837234</v>
+        <v>1.753821803061814</v>
       </c>
       <c r="G66">
-        <v>-5.756609472540823</v>
+        <v>-5.597623833562864</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.448877912326383</v>
       </c>
       <c r="E67">
-        <v>-11.78329975447022</v>
+        <v>-15.13245044716704</v>
       </c>
       <c r="F67">
-        <v>2.018788370725681</v>
+        <v>1.894594559493562</v>
       </c>
       <c r="G67">
-        <v>-5.273104296530266</v>
+        <v>-6.062954114562822</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.06730892030969</v>
       </c>
       <c r="E68">
-        <v>-13.68286327494172</v>
+        <v>-14.14039311783268</v>
       </c>
       <c r="F68">
-        <v>1.992833963261166</v>
+        <v>1.801053655634636</v>
       </c>
       <c r="G68">
-        <v>-5.336289368692796</v>
+        <v>-6.074266248670511</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.620667930689181</v>
       </c>
       <c r="E69">
-        <v>-13.70974882512526</v>
+        <v>-14.54388920886413</v>
       </c>
       <c r="F69">
-        <v>1.585254006796531</v>
+        <v>1.743970857907722</v>
       </c>
       <c r="G69">
-        <v>-5.451440074185266</v>
+        <v>-6.016722346106899</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.106489897209075</v>
       </c>
       <c r="E70">
-        <v>-13.93403508577715</v>
+        <v>-13.83501094465143</v>
       </c>
       <c r="F70">
-        <v>1.69384800309913</v>
+        <v>1.593560875111805</v>
       </c>
       <c r="G70">
-        <v>-6.315836756671129</v>
+        <v>-6.992048788522663</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.53517169320377</v>
       </c>
       <c r="E71">
-        <v>-13.30283373621802</v>
+        <v>-13.76445731961192</v>
       </c>
       <c r="F71">
-        <v>1.058329501875766</v>
+        <v>1.581658892268381</v>
       </c>
       <c r="G71">
-        <v>-5.973317783541515</v>
+        <v>-5.886475552955353</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.916865023366659</v>
       </c>
       <c r="E72">
-        <v>-13.57970463704699</v>
+        <v>-14.42866671621296</v>
       </c>
       <c r="F72">
-        <v>1.713192038689304</v>
+        <v>1.418157391038621</v>
       </c>
       <c r="G72">
-        <v>-5.594942291676054</v>
+        <v>-6.442266490815896</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.25803434927905</v>
       </c>
       <c r="E73">
-        <v>-13.56637733804241</v>
+        <v>-15.09980920651975</v>
       </c>
       <c r="F73">
-        <v>1.303990138849987</v>
+        <v>1.209778257394794</v>
       </c>
       <c r="G73">
-        <v>-4.761757432534439</v>
+        <v>-6.150815993175079</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.579232016275865</v>
       </c>
       <c r="E74">
-        <v>-13.046005861347</v>
+        <v>-15.20239272821551</v>
       </c>
       <c r="F74">
-        <v>0.8475464460290149</v>
+        <v>0.9293692646079388</v>
       </c>
       <c r="G74">
-        <v>-5.664291599632707</v>
+        <v>-6.168077177616839</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.893559047881383</v>
       </c>
       <c r="E75">
-        <v>-14.6967840767851</v>
+        <v>-15.26069230259025</v>
       </c>
       <c r="F75">
-        <v>1.106310198580719</v>
+        <v>1.321379227369554</v>
       </c>
       <c r="G75">
-        <v>-5.275067450035054</v>
+        <v>-6.190479639281087</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.211400402958702</v>
       </c>
       <c r="E76">
-        <v>-13.87162365700344</v>
+        <v>-14.65290316365078</v>
       </c>
       <c r="F76">
-        <v>1.02873193457374</v>
+        <v>1.400007861243284</v>
       </c>
       <c r="G76">
-        <v>-5.726202111762617</v>
+        <v>-6.114568830065599</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.549283387987898</v>
       </c>
       <c r="E77">
-        <v>-15.46397550079458</v>
+        <v>-15.57241433938225</v>
       </c>
       <c r="F77">
-        <v>0.4115236664218558</v>
+        <v>1.043753549056106</v>
       </c>
       <c r="G77">
-        <v>-4.481807770097049</v>
+        <v>-5.701574963495979</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.9141247369811381</v>
       </c>
       <c r="E78">
-        <v>-15.64920367313032</v>
+        <v>-15.46909267642324</v>
       </c>
       <c r="F78">
-        <v>0.7306903132508942</v>
+        <v>1.110841368274032</v>
       </c>
       <c r="G78">
-        <v>-4.506160143083928</v>
+        <v>-5.708431103307809</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.3140633070611769</v>
       </c>
       <c r="E79">
-        <v>-15.56989197935998</v>
+        <v>-16.08530024854298</v>
       </c>
       <c r="F79">
-        <v>0.3634369386893446</v>
+        <v>0.856284065393744</v>
       </c>
       <c r="G79">
-        <v>-4.620519628192512</v>
+        <v>-4.957192177899774</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.2419786729485201</v>
       </c>
       <c r="E80">
-        <v>-16.69137309583355</v>
+        <v>-17.10281213027445</v>
       </c>
       <c r="F80">
-        <v>0.3473757231164649</v>
+        <v>1.00648364286935</v>
       </c>
       <c r="G80">
-        <v>-4.258276424739919</v>
+        <v>-5.226693758615223</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.7541107729557874</v>
       </c>
       <c r="E81">
-        <v>-16.99420120967448</v>
+        <v>-17.30869014408517</v>
       </c>
       <c r="F81">
-        <v>0.2730214650411813</v>
+        <v>0.9793479834884442</v>
       </c>
       <c r="G81">
-        <v>-4.680980121376222</v>
+        <v>-4.475504491390277</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.218341484255222</v>
       </c>
       <c r="E82">
-        <v>-19.40484830665165</v>
+        <v>-16.85418079335732</v>
       </c>
       <c r="F82">
-        <v>1.133628098790241</v>
+        <v>0.9060788867108279</v>
       </c>
       <c r="G82">
-        <v>-4.284363523589376</v>
+        <v>-4.055882912651036</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.63284314460853</v>
       </c>
       <c r="E83">
-        <v>-18.74098307407519</v>
+        <v>-19.1382570418201</v>
       </c>
       <c r="F83">
-        <v>0.3463079575342564</v>
+        <v>0.7819380909924883</v>
       </c>
       <c r="G83">
-        <v>-3.968765906785115</v>
+        <v>-3.18086600007519</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.002646013175893</v>
       </c>
       <c r="E84">
-        <v>-19.39913790092798</v>
+        <v>-20.64934089106958</v>
       </c>
       <c r="F84">
-        <v>0.361947534099111</v>
+        <v>0.5820513799621621</v>
       </c>
       <c r="G84">
-        <v>-3.655260554761673</v>
+        <v>-3.994872868907807</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.32525873214815</v>
       </c>
       <c r="E85">
-        <v>-20.68995224597037</v>
+        <v>-20.87550193996065</v>
       </c>
       <c r="F85">
-        <v>0.4241960309498827</v>
+        <v>0.3830907836881656</v>
       </c>
       <c r="G85">
-        <v>-3.407012676408344</v>
+        <v>-3.477590196760067</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.600155545562301</v>
       </c>
       <c r="E86">
-        <v>-20.77370637274223</v>
+        <v>-21.63102348645236</v>
       </c>
       <c r="F86">
-        <v>-0.2725214256249059</v>
+        <v>0.2388156898773813</v>
       </c>
       <c r="G86">
-        <v>-3.538626724867609</v>
+        <v>-3.324030541920973</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.826877118184086</v>
       </c>
       <c r="E87">
-        <v>-24.01160604449261</v>
+        <v>-22.91621346677722</v>
       </c>
       <c r="F87">
-        <v>-0.2802948253327764</v>
+        <v>0.3662823807179608</v>
       </c>
       <c r="G87">
-        <v>-2.525103208019735</v>
+        <v>-3.486412800622224</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.000653083219504</v>
       </c>
       <c r="E88">
-        <v>-23.43213345352309</v>
+        <v>-24.88376749599988</v>
       </c>
       <c r="F88">
-        <v>-0.2799063210208635</v>
+        <v>0.2384984251621091</v>
       </c>
       <c r="G88">
-        <v>-2.132611549974822</v>
+        <v>-2.422532575576496</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.117045191254347</v>
       </c>
       <c r="E89">
-        <v>-25.45400652846775</v>
+        <v>-26.08552939968143</v>
       </c>
       <c r="F89">
-        <v>-0.5623696649666613</v>
+        <v>-0.006248522566824423</v>
       </c>
       <c r="G89">
-        <v>-2.020721731838535</v>
+        <v>-3.229435013681837</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.170411417317684</v>
       </c>
       <c r="E90">
-        <v>-27.04009549270628</v>
+        <v>-26.98524661552538</v>
       </c>
       <c r="F90">
-        <v>-0.5957064827249247</v>
+        <v>-0.2960884782345519</v>
       </c>
       <c r="G90">
-        <v>-2.679970528346842</v>
+        <v>-2.474561109271682</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.154787103861304</v>
       </c>
       <c r="E91">
-        <v>-28.10703566823147</v>
+        <v>-28.20938370927883</v>
       </c>
       <c r="F91">
-        <v>-0.7583506236927879</v>
+        <v>-0.03640937970275442</v>
       </c>
       <c r="G91">
-        <v>-3.363498865840163</v>
+        <v>-3.348005512716374</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.064712754026303</v>
       </c>
       <c r="E92">
-        <v>-29.90081630012079</v>
+        <v>-29.42123505304947</v>
       </c>
       <c r="F92">
-        <v>-1.233112004891866</v>
+        <v>-1.026753259343467</v>
       </c>
       <c r="G92">
-        <v>-2.804781405722905</v>
+        <v>-3.53231020397868</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.896900051769268</v>
       </c>
       <c r="E93">
-        <v>-31.22157065106489</v>
+        <v>-31.05496582808569</v>
       </c>
       <c r="F93">
-        <v>-1.495546253405374</v>
+        <v>-0.9747591225719504</v>
       </c>
       <c r="G93">
-        <v>-2.550068031931379</v>
+        <v>-3.329721369702979</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.651145710381033</v>
       </c>
       <c r="E94">
-        <v>-34.5836501370536</v>
+        <v>-33.81868445801889</v>
       </c>
       <c r="F94">
-        <v>-1.259174100118744</v>
+        <v>-0.7731568626504263</v>
       </c>
       <c r="G94">
-        <v>-2.546436363474799</v>
+        <v>-3.513605621681798</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.329754682444183</v>
       </c>
       <c r="E95">
-        <v>-35.22474167384549</v>
+        <v>-35.01496011544015</v>
       </c>
       <c r="F95">
-        <v>-1.034904394587014</v>
+        <v>-1.045633409188073</v>
       </c>
       <c r="G95">
-        <v>-2.723732629830467</v>
+        <v>-3.964627724861026</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.938693728651545</v>
       </c>
       <c r="E96">
-        <v>-37.62881569080052</v>
+        <v>-38.4201597309299</v>
       </c>
       <c r="F96">
-        <v>-1.658876282582756</v>
+        <v>-1.439539504934697</v>
       </c>
       <c r="G96">
-        <v>-2.593701022138974</v>
+        <v>-3.379614601525336</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.49307849206323</v>
       </c>
       <c r="E97">
-        <v>-40.34185843235089</v>
+        <v>-39.51597119249099</v>
       </c>
       <c r="F97">
-        <v>-1.984617681487814</v>
+        <v>-1.2718845695473</v>
       </c>
       <c r="G97">
-        <v>-3.558665457016818</v>
+        <v>-3.645842052702446</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.00080154888876</v>
       </c>
       <c r="E98">
-        <v>-41.67653557663157</v>
+        <v>-42.03697267256108</v>
       </c>
       <c r="F98">
-        <v>-1.775838446388435</v>
+        <v>-1.42543489316723</v>
       </c>
       <c r="G98">
-        <v>-3.164627774205065</v>
+        <v>-3.925692398773657</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.4955268533360727</v>
       </c>
       <c r="E99">
-        <v>-44.76845988874469</v>
+        <v>-43.78483457801262</v>
       </c>
       <c r="F99">
-        <v>-2.35062436310815</v>
+        <v>-1.842708404979425</v>
       </c>
       <c r="G99">
-        <v>-2.664089841394958</v>
+        <v>-4.711857579621004</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.01982097889383494</v>
       </c>
       <c r="E100">
-        <v>-46.00712659135176</v>
+        <v>-46.07092146893481</v>
       </c>
       <c r="F100">
-        <v>-2.185503403605916</v>
+        <v>-1.912574568466341</v>
       </c>
       <c r="G100">
-        <v>-4.537646741707936</v>
+        <v>-4.920521264961267</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.4890072864663929</v>
       </c>
       <c r="E101">
-        <v>-48.4971046281138</v>
+        <v>-48.16538145374842</v>
       </c>
       <c r="F101">
-        <v>-2.084614052516756</v>
+        <v>-1.631213781533669</v>
       </c>
       <c r="G101">
-        <v>-4.132045323327509</v>
+        <v>-4.997246468379416</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.9367493950446174</v>
       </c>
       <c r="E102">
-        <v>-49.28213823971349</v>
+        <v>-50.08823718027837</v>
       </c>
       <c r="F102">
-        <v>-2.501132093257598</v>
+        <v>-2.107164698323167</v>
       </c>
       <c r="G102">
-        <v>-3.762614925509159</v>
+        <v>-4.841038377108905</v>
       </c>
     </row>
   </sheetData>
